--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/0.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/0.xlsx
@@ -426,13 +426,13 @@
         <v>-16.12213587338557</v>
       </c>
       <c r="E2">
-        <v>-11.58464918517575</v>
+        <v>-5.931030525559615</v>
       </c>
       <c r="F2">
-        <v>-1.764983874373638</v>
+        <v>-1.683166459370205</v>
       </c>
       <c r="G2">
-        <v>-10.70284259403727</v>
+        <v>-10.07111105205139</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.88127131520539</v>
       </c>
       <c r="E3">
-        <v>-12.42008924095482</v>
+        <v>-7.462252498721208</v>
       </c>
       <c r="F3">
-        <v>-1.604038177011188</v>
+        <v>-1.534460433175229</v>
       </c>
       <c r="G3">
-        <v>-10.63291063006571</v>
+        <v>-9.540738482841371</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.60155082846408</v>
       </c>
       <c r="E4">
-        <v>-12.7411852189427</v>
+        <v>-8.242811978001324</v>
       </c>
       <c r="F4">
-        <v>-2.110715586096604</v>
+        <v>-1.712134024269508</v>
       </c>
       <c r="G4">
-        <v>-9.753540350105723</v>
+        <v>-8.792253931322008</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.29304962904582</v>
       </c>
       <c r="E5">
-        <v>-13.15619269090164</v>
+        <v>-9.090655524087408</v>
       </c>
       <c r="F5">
-        <v>-1.835350303755485</v>
+        <v>-1.596098267404133</v>
       </c>
       <c r="G5">
-        <v>-9.376316928087927</v>
+        <v>-9.071534863560466</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.94236281859554</v>
       </c>
       <c r="E6">
-        <v>-14.41415748549239</v>
+        <v>-11.19547212895656</v>
       </c>
       <c r="F6">
-        <v>-1.564631614570266</v>
+        <v>-1.655930676889435</v>
       </c>
       <c r="G6">
-        <v>-9.433059678631036</v>
+        <v>-7.626730026584038</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.55600601626386</v>
       </c>
       <c r="E7">
-        <v>-14.45576057620086</v>
+        <v>-9.170492520842636</v>
       </c>
       <c r="F7">
-        <v>-1.882415668003473</v>
+        <v>-1.429918421991156</v>
       </c>
       <c r="G7">
-        <v>-8.716958883576826</v>
+        <v>-9.777667605995932</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.14721113168351</v>
       </c>
       <c r="E8">
-        <v>-16.34035296160299</v>
+        <v>-11.29216863444234</v>
       </c>
       <c r="F8">
-        <v>-1.556739216140674</v>
+        <v>-1.449203208923462</v>
       </c>
       <c r="G8">
-        <v>-8.773483138114342</v>
+        <v>-8.575529067593621</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.74365278740791</v>
       </c>
       <c r="E9">
-        <v>-16.66267162757293</v>
+        <v>-10.98943561855557</v>
       </c>
       <c r="F9">
-        <v>-1.419647297276573</v>
+        <v>-1.028412547191201</v>
       </c>
       <c r="G9">
-        <v>-9.023561748150888</v>
+        <v>-8.152176504031621</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.37704283472204</v>
       </c>
       <c r="E10">
-        <v>-17.69572523209873</v>
+        <v>-12.35624681439469</v>
       </c>
       <c r="F10">
-        <v>-1.422188353417896</v>
+        <v>-1.146260855476797</v>
       </c>
       <c r="G10">
-        <v>-8.343403546016543</v>
+        <v>-7.262718991813474</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.07938512770513</v>
       </c>
       <c r="E11">
-        <v>-18.36891006418297</v>
+        <v>-13.05683344269934</v>
       </c>
       <c r="F11">
-        <v>-1.012444832298783</v>
+        <v>-1.19061887446234</v>
       </c>
       <c r="G11">
-        <v>-7.590214709285877</v>
+        <v>-7.777598207899705</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.87949421641912</v>
       </c>
       <c r="E12">
-        <v>-18.65722894730333</v>
+        <v>-14.60911734847061</v>
       </c>
       <c r="F12">
-        <v>-1.316973267219761</v>
+        <v>-0.7587517735574955</v>
       </c>
       <c r="G12">
-        <v>-7.002268442602393</v>
+        <v>-6.619513098988476</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.79182880536639</v>
       </c>
       <c r="E13">
-        <v>-19.50456077582654</v>
+        <v>-14.67010230793191</v>
       </c>
       <c r="F13">
-        <v>-0.8357040439886982</v>
+        <v>-0.6429717851974638</v>
       </c>
       <c r="G13">
-        <v>-6.913621964697328</v>
+        <v>-6.317991921817195</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.81212796464902</v>
       </c>
       <c r="E14">
-        <v>-19.57753713446015</v>
+        <v>-14.87042388413522</v>
       </c>
       <c r="F14">
-        <v>-0.8054164602088765</v>
+        <v>-0.8959228777173678</v>
       </c>
       <c r="G14">
-        <v>-5.850052930932291</v>
+        <v>-6.113410139126854</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.91119658399058</v>
       </c>
       <c r="E15">
-        <v>-20.65869671836943</v>
+        <v>-16.58576455350067</v>
       </c>
       <c r="F15">
-        <v>-0.4102097756875819</v>
+        <v>-0.3658644263493619</v>
       </c>
       <c r="G15">
-        <v>-6.723292080553549</v>
+        <v>-5.181395564001376</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.0435272301802</v>
       </c>
       <c r="E16">
-        <v>-20.96853943844824</v>
+        <v>-16.5264506009482</v>
       </c>
       <c r="F16">
-        <v>0.1529243737243768</v>
+        <v>-0.2308772526468806</v>
       </c>
       <c r="G16">
-        <v>-6.109672533213017</v>
+        <v>-4.560767591754206</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.1577478772837</v>
       </c>
       <c r="E17">
-        <v>-21.46259595268508</v>
+        <v>-17.83311460501744</v>
       </c>
       <c r="F17">
-        <v>-0.08964552651982158</v>
+        <v>-0.1351580671177204</v>
       </c>
       <c r="G17">
-        <v>-6.074934978869444</v>
+        <v>-4.662113322347915</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.20807672153663</v>
       </c>
       <c r="E18">
-        <v>-23.27595997042057</v>
+        <v>-18.18612726781138</v>
       </c>
       <c r="F18">
-        <v>0.03228715932169236</v>
+        <v>0.03842797900880882</v>
       </c>
       <c r="G18">
-        <v>-5.444984510383687</v>
+        <v>-4.818536599078478</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.16107498199292</v>
       </c>
       <c r="E19">
-        <v>-23.72641633691155</v>
+        <v>-19.49525023326677</v>
       </c>
       <c r="F19">
-        <v>0.4420306804408057</v>
+        <v>0.6693772075728424</v>
       </c>
       <c r="G19">
-        <v>-5.406664945766622</v>
+        <v>-3.609234040129185</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.99778851644904</v>
       </c>
       <c r="E20">
-        <v>-24.58110693569723</v>
+        <v>-20.74598758334128</v>
       </c>
       <c r="F20">
-        <v>0.6138825685899287</v>
+        <v>1.022644983894427</v>
       </c>
       <c r="G20">
-        <v>-4.886896053918889</v>
+        <v>-4.302852920426206</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.71815306177959</v>
       </c>
       <c r="E21">
-        <v>-24.94443546228064</v>
+        <v>-21.31469599159456</v>
       </c>
       <c r="F21">
-        <v>0.7471419191386656</v>
+        <v>0.8951566577015517</v>
       </c>
       <c r="G21">
-        <v>-5.134435475526814</v>
+        <v>-3.905461654983171</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.3392351869718</v>
       </c>
       <c r="E22">
-        <v>-26.40754012941886</v>
+        <v>-22.80301067353348</v>
       </c>
       <c r="F22">
-        <v>0.7551649733062819</v>
+        <v>0.7085549245089835</v>
       </c>
       <c r="G22">
-        <v>-5.001712394311893</v>
+        <v>-3.469297280184192</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.89095987905007</v>
       </c>
       <c r="E23">
-        <v>-26.07356517135317</v>
+        <v>-22.51139506133554</v>
       </c>
       <c r="F23">
-        <v>0.9229237735169517</v>
+        <v>1.143000298644164</v>
       </c>
       <c r="G23">
-        <v>-5.099535704451817</v>
+        <v>-4.5500778402079</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.4056990631818</v>
       </c>
       <c r="E24">
-        <v>-26.9389157979529</v>
+        <v>-23.16272547785877</v>
       </c>
       <c r="F24">
-        <v>1.112669162951667</v>
+        <v>1.130717075564015</v>
       </c>
       <c r="G24">
-        <v>-4.754689417808095</v>
+        <v>-3.356242150018081</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.91464594920749</v>
       </c>
       <c r="E25">
-        <v>-27.56228288747877</v>
+        <v>-23.77397889941411</v>
       </c>
       <c r="F25">
-        <v>1.031960342089042</v>
+        <v>1.233743480187013</v>
       </c>
       <c r="G25">
-        <v>-4.882337432711313</v>
+        <v>-3.944224832702497</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.44821576413106</v>
       </c>
       <c r="E26">
-        <v>-26.59957006971412</v>
+        <v>-23.57581740531246</v>
       </c>
       <c r="F26">
-        <v>1.049295587039442</v>
+        <v>0.7069300422397425</v>
       </c>
       <c r="G26">
-        <v>-4.773281441556642</v>
+        <v>-2.941195745214113</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.03345060976102</v>
       </c>
       <c r="E27">
-        <v>-26.7046487805881</v>
+        <v>-23.63038098863089</v>
       </c>
       <c r="F27">
-        <v>0.7342901456348745</v>
+        <v>0.8021297722286387</v>
       </c>
       <c r="G27">
-        <v>-4.152434973303881</v>
+        <v>-4.00721789322375</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.690454704544326</v>
       </c>
       <c r="E28">
-        <v>-27.52982278579178</v>
+        <v>-23.0124933526543</v>
       </c>
       <c r="F28">
-        <v>0.7597814760497879</v>
+        <v>0.7499339926675853</v>
       </c>
       <c r="G28">
-        <v>-5.182123884020015</v>
+        <v>-3.823419715428952</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.430457559805966</v>
       </c>
       <c r="E29">
-        <v>-28.30222195491008</v>
+        <v>-22.79497263216987</v>
       </c>
       <c r="F29">
-        <v>0.5445336702587508</v>
+        <v>0.8656823069093083</v>
       </c>
       <c r="G29">
-        <v>-4.362280523401663</v>
+        <v>-3.00807207565293</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.254658140953524</v>
       </c>
       <c r="E30">
-        <v>-27.69898393234831</v>
+        <v>-24.73213607232704</v>
       </c>
       <c r="F30">
-        <v>0.7671362063210886</v>
+        <v>0.1464185098237516</v>
       </c>
       <c r="G30">
-        <v>-3.851814264519282</v>
+        <v>-2.368964638205549</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.153663257042281</v>
       </c>
       <c r="E31">
-        <v>-27.20085631997858</v>
+        <v>-23.86673110403922</v>
       </c>
       <c r="F31">
-        <v>0.6435881404458265</v>
+        <v>0.4286269854254839</v>
       </c>
       <c r="G31">
-        <v>-4.054605042072877</v>
+        <v>-3.403510119227795</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.112905145371927</v>
       </c>
       <c r="E32">
-        <v>-28.04540313698708</v>
+        <v>-22.49356193069333</v>
       </c>
       <c r="F32">
-        <v>0.7068540243558015</v>
+        <v>0.2092813405782473</v>
       </c>
       <c r="G32">
-        <v>-4.408704303498863</v>
+        <v>-3.468919877992715</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.119675096830372</v>
       </c>
       <c r="E33">
-        <v>-27.10044193733249</v>
+        <v>-23.70453475050649</v>
       </c>
       <c r="F33">
-        <v>0.6405901851478996</v>
+        <v>0.4900613134442532</v>
       </c>
       <c r="G33">
-        <v>-4.256531767240723</v>
+        <v>-3.144522831145071</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.163138797674776</v>
       </c>
       <c r="E34">
-        <v>-26.80500429307208</v>
+        <v>-22.69749722915476</v>
       </c>
       <c r="F34">
-        <v>0.3490932743521148</v>
+        <v>0.6891228529265414</v>
       </c>
       <c r="G34">
-        <v>-3.99054598588798</v>
+        <v>-2.5470686776728</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.231283825300272</v>
       </c>
       <c r="E35">
-        <v>-26.49666049788981</v>
+        <v>-22.49154675975992</v>
       </c>
       <c r="F35">
-        <v>0.4680683893965457</v>
+        <v>0.6818188012445346</v>
       </c>
       <c r="G35">
-        <v>-4.085376562860403</v>
+        <v>-2.347399744562737</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.307769449097446</v>
       </c>
       <c r="E36">
-        <v>-26.43839262283311</v>
+        <v>-23.27797514135398</v>
       </c>
       <c r="F36">
-        <v>0.4255664737438972</v>
+        <v>0.5561501531484991</v>
       </c>
       <c r="G36">
-        <v>-3.377025754913626</v>
+        <v>-2.425806705114836</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.373292015426594</v>
       </c>
       <c r="E37">
-        <v>-25.45004411371104</v>
+        <v>-22.01719816440447</v>
       </c>
       <c r="F37">
-        <v>0.9624182316361806</v>
+        <v>0.6995373030264712</v>
       </c>
       <c r="G37">
-        <v>-3.680271726310866</v>
+        <v>-2.136398814071748</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.412270311700206</v>
       </c>
       <c r="E38">
-        <v>-25.26596617377325</v>
+        <v>-20.77017869149025</v>
       </c>
       <c r="F38">
-        <v>0.6255592323044638</v>
+        <v>0.6533089273547937</v>
       </c>
       <c r="G38">
-        <v>-3.688604369433212</v>
+        <v>-2.619486861344357</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.415663320202944</v>
       </c>
       <c r="E39">
-        <v>-25.58659571893833</v>
+        <v>-20.32740261691628</v>
       </c>
       <c r="F39">
-        <v>1.028683654549998</v>
+        <v>0.8221430638820469</v>
       </c>
       <c r="G39">
-        <v>-3.343095973681635</v>
+        <v>-1.469625147552678</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.382649922473838</v>
       </c>
       <c r="E40">
-        <v>-24.45990685735594</v>
+        <v>-20.65539546081784</v>
       </c>
       <c r="F40">
-        <v>0.7142214242744258</v>
+        <v>0.8518027082663969</v>
       </c>
       <c r="G40">
-        <v>-3.293805261147427</v>
+        <v>-2.976290838475927</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.315742892994702</v>
       </c>
       <c r="E41">
-        <v>-25.33740285124425</v>
+        <v>-20.28208164904752</v>
       </c>
       <c r="F41">
-        <v>0.8275735914660888</v>
+        <v>0.7711952445823599</v>
       </c>
       <c r="G41">
-        <v>-3.472727005362877</v>
+        <v>-2.847801945005734</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.219113558784626</v>
       </c>
       <c r="E42">
-        <v>-24.80503091842851</v>
+        <v>-20.59113641464899</v>
       </c>
       <c r="F42">
-        <v>0.8608710083382032</v>
+        <v>0.9913271994166122</v>
       </c>
       <c r="G42">
-        <v>-3.837863625616793</v>
+        <v>-2.587526854708233</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.095764205708798</v>
       </c>
       <c r="E43">
-        <v>-23.54813031522957</v>
+        <v>-19.79331892092565</v>
       </c>
       <c r="F43">
-        <v>0.8527133391677746</v>
+        <v>1.064936266660322</v>
       </c>
       <c r="G43">
-        <v>-3.820817626635086</v>
+        <v>-2.774559435494898</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.949373502362217</v>
       </c>
       <c r="E44">
-        <v>-23.73704466540755</v>
+        <v>-19.46851412272549</v>
       </c>
       <c r="F44">
-        <v>1.019365128943552</v>
+        <v>0.79626055810602</v>
       </c>
       <c r="G44">
-        <v>-4.280870898045445</v>
+        <v>-2.734296580646282</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.784750374437056</v>
       </c>
       <c r="E45">
-        <v>-24.16977658463252</v>
+        <v>-19.49707067981786</v>
       </c>
       <c r="F45">
-        <v>1.052787658582986</v>
+        <v>0.8282403316564888</v>
       </c>
       <c r="G45">
-        <v>-4.212769665757097</v>
+        <v>-2.821158674505679</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.609323453868178</v>
       </c>
       <c r="E46">
-        <v>-23.72114972164063</v>
+        <v>-18.53703419019174</v>
       </c>
       <c r="F46">
-        <v>1.132815485901973</v>
+        <v>1.08344978881181</v>
       </c>
       <c r="G46">
-        <v>-4.555523687620001</v>
+        <v>-3.201712505335981</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.434914488128985</v>
       </c>
       <c r="E47">
-        <v>-23.16833172868026</v>
+        <v>-18.44091732937894</v>
       </c>
       <c r="F47">
-        <v>0.9405836781800169</v>
+        <v>1.075718136532634</v>
       </c>
       <c r="G47">
-        <v>-4.562124915425307</v>
+        <v>-3.039174650994383</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.273418368822689</v>
       </c>
       <c r="E48">
-        <v>-21.95712795669272</v>
+        <v>-18.03804616776055</v>
       </c>
       <c r="F48">
-        <v>1.056583801662295</v>
+        <v>1.114083412334155</v>
       </c>
       <c r="G48">
-        <v>-5.829967851145534</v>
+        <v>-3.706481315345276</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.133913138401521</v>
       </c>
       <c r="E49">
-        <v>-22.25610686762713</v>
+        <v>-18.03261652742536</v>
       </c>
       <c r="F49">
-        <v>0.9285823547528168</v>
+        <v>0.8814259274146917</v>
       </c>
       <c r="G49">
-        <v>-4.920739760966859</v>
+        <v>-4.200669621811062</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.021362180929549</v>
       </c>
       <c r="E50">
-        <v>-22.04356746855113</v>
+        <v>-18.46223285653304</v>
       </c>
       <c r="F50">
-        <v>1.21371435147445</v>
+        <v>1.1100671341326</v>
       </c>
       <c r="G50">
-        <v>-5.26273235735573</v>
+        <v>-4.29488443731318</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.940280226044741</v>
       </c>
       <c r="E51">
-        <v>-20.94197088144524</v>
+        <v>-18.18612273933737</v>
       </c>
       <c r="F51">
-        <v>1.372480869497255</v>
+        <v>1.017071922777996</v>
       </c>
       <c r="G51">
-        <v>-6.099532332226229</v>
+        <v>-3.859984690910203</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.892094484531288</v>
       </c>
       <c r="E52">
-        <v>-20.91020816475544</v>
+        <v>-15.59665978921932</v>
       </c>
       <c r="F52">
-        <v>0.9977808010220279</v>
+        <v>1.151625161059647</v>
       </c>
       <c r="G52">
-        <v>-5.473650524208236</v>
+        <v>-4.18159756895932</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.875725338488288</v>
       </c>
       <c r="E53">
-        <v>-21.62203446554713</v>
+        <v>-17.2376882001189</v>
       </c>
       <c r="F53">
-        <v>1.028016914359598</v>
+        <v>1.144748709974809</v>
       </c>
       <c r="G53">
-        <v>-5.956424069654614</v>
+        <v>-4.597875496703897</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.888645270623063</v>
       </c>
       <c r="E54">
-        <v>-20.09884600527515</v>
+        <v>-15.78942787077783</v>
       </c>
       <c r="F54">
-        <v>1.374523850128172</v>
+        <v>1.128287670689731</v>
       </c>
       <c r="G54">
-        <v>-6.496642201298426</v>
+        <v>-4.494275284597944</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.927582004377712</v>
       </c>
       <c r="E55">
-        <v>-20.80395205063946</v>
+        <v>-15.51713072869661</v>
       </c>
       <c r="F55">
-        <v>1.034487936730083</v>
+        <v>1.145139885335922</v>
       </c>
       <c r="G55">
-        <v>-6.263036865865294</v>
+        <v>-5.254194460409949</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.988582568983929</v>
       </c>
       <c r="E56">
-        <v>-20.19743994137015</v>
+        <v>-16.07600329140523</v>
       </c>
       <c r="F56">
-        <v>0.8519610788579408</v>
+        <v>0.9197832846866352</v>
       </c>
       <c r="G56">
-        <v>-6.740155999530597</v>
+        <v>-5.051784395593369</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.066883227833754</v>
       </c>
       <c r="E57">
-        <v>-19.9952616908237</v>
+        <v>-15.08591131979021</v>
       </c>
       <c r="F57">
-        <v>0.9382382097192511</v>
+        <v>0.7760556380368435</v>
       </c>
       <c r="G57">
-        <v>-6.448841234256889</v>
+        <v>-5.13449506534652</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.159415402056448</v>
       </c>
       <c r="E58">
-        <v>-20.02881315474653</v>
+        <v>-14.69154916083224</v>
       </c>
       <c r="F58">
-        <v>0.9775473742463736</v>
+        <v>1.010756103587223</v>
       </c>
       <c r="G58">
-        <v>-6.499492581007738</v>
+        <v>-5.344790849637644</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.264041713657836</v>
       </c>
       <c r="E59">
-        <v>-19.66530801767682</v>
+        <v>-13.58710416357552</v>
       </c>
       <c r="F59">
-        <v>1.087339370540129</v>
+        <v>0.4997733899706857</v>
       </c>
       <c r="G59">
-        <v>-5.914141782027042</v>
+        <v>-5.587559775123479</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.382354307370763</v>
       </c>
       <c r="E60">
-        <v>-19.97624662846549</v>
+        <v>-14.08781300612962</v>
       </c>
       <c r="F60">
-        <v>0.7688941198872264</v>
+        <v>0.8195283654156564</v>
       </c>
       <c r="G60">
-        <v>-6.533021786229477</v>
+        <v>-6.050956697528503</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.516608120075313</v>
       </c>
       <c r="E61">
-        <v>-19.75380798520872</v>
+        <v>-14.37994486436444</v>
       </c>
       <c r="F61">
-        <v>0.8366244707728252</v>
+        <v>0.6099438919782308</v>
       </c>
       <c r="G61">
-        <v>-7.381140516298744</v>
+        <v>-5.378459097772033</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.668293051286529</v>
       </c>
       <c r="E62">
-        <v>-19.9211667991102</v>
+        <v>-15.03519693937831</v>
       </c>
       <c r="F62">
-        <v>1.205281117474735</v>
+        <v>1.117817790882761</v>
       </c>
       <c r="G62">
-        <v>-7.221995971134899</v>
+        <v>-5.449251803583808</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.83810577995324</v>
       </c>
       <c r="E63">
-        <v>-18.76151517522597</v>
+        <v>-14.2803229646697</v>
       </c>
       <c r="F63">
-        <v>0.5594046688047272</v>
+        <v>0.282108848952688</v>
       </c>
       <c r="G63">
-        <v>-7.29294758313256</v>
+        <v>-6.666354007823624</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.026485596450666</v>
       </c>
       <c r="E64">
-        <v>-18.99011254313317</v>
+        <v>-13.56047673641042</v>
       </c>
       <c r="F64">
-        <v>0.4502612000833445</v>
+        <v>0.9422861620391143</v>
       </c>
       <c r="G64">
-        <v>-8.577359799276838</v>
+        <v>-6.359281045782986</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.233516892812624</v>
       </c>
       <c r="E65">
-        <v>-18.51431936456927</v>
+        <v>-13.41343718538136</v>
       </c>
       <c r="F65">
-        <v>0.8673515329441814</v>
+        <v>0.6459969571432098</v>
       </c>
       <c r="G65">
-        <v>-8.03231158169123</v>
+        <v>-7.444944660477118</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.457913248432229</v>
       </c>
       <c r="E66">
-        <v>-19.68011159920789</v>
+        <v>-13.81669779576441</v>
       </c>
       <c r="F66">
-        <v>0.9755724929698206</v>
+        <v>0.6468141493955766</v>
       </c>
       <c r="G66">
-        <v>-7.971463754679426</v>
+        <v>-6.332611290918617</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.698903070297911</v>
       </c>
       <c r="E67">
-        <v>-18.559622218542</v>
+        <v>-13.60769060641439</v>
       </c>
       <c r="F67">
-        <v>0.6220196495834566</v>
+        <v>0.5406361700008543</v>
       </c>
       <c r="G67">
-        <v>-8.10498798791485</v>
+        <v>-7.040458895943425</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.95403965254261</v>
       </c>
       <c r="E68">
-        <v>-18.06477774982783</v>
+        <v>-13.02678701765845</v>
       </c>
       <c r="F68">
-        <v>0.645168678949435</v>
+        <v>0.4679171454816212</v>
       </c>
       <c r="G68">
-        <v>-8.142661996151755</v>
+        <v>-6.133478666185916</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.21943072281306</v>
       </c>
       <c r="E69">
-        <v>-18.73938452275048</v>
+        <v>-14.19763755776365</v>
       </c>
       <c r="F69">
-        <v>0.5877118283372919</v>
+        <v>0.8844191315948723</v>
       </c>
       <c r="G69">
-        <v>-8.331455787165313</v>
+        <v>-7.652757535613788</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.48835961219233</v>
       </c>
       <c r="E70">
-        <v>-18.6549692387735</v>
+        <v>-13.04245100925098</v>
       </c>
       <c r="F70">
-        <v>0.4635841260969789</v>
+        <v>0.1574696097016881</v>
       </c>
       <c r="G70">
-        <v>-8.694546490275959</v>
+        <v>-7.564415627898336</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.75288276417475</v>
       </c>
       <c r="E71">
-        <v>-18.10190670821672</v>
+        <v>-13.49834607302518</v>
       </c>
       <c r="F71">
-        <v>0.5692632381283377</v>
+        <v>0.7290290745837846</v>
       </c>
       <c r="G71">
-        <v>-8.708818252095757</v>
+        <v>-7.325596183240852</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.00500369764277</v>
       </c>
       <c r="E72">
-        <v>-19.354278837408</v>
+        <v>-14.09308867834856</v>
       </c>
       <c r="F72">
-        <v>0.6190327802269378</v>
+        <v>0.6479528339487776</v>
       </c>
       <c r="G72">
-        <v>-9.295559480202947</v>
+        <v>-7.610213714888614</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.23655509791738</v>
       </c>
       <c r="E73">
-        <v>-18.29682581492888</v>
+        <v>-13.32742335007967</v>
       </c>
       <c r="F73">
-        <v>0.5965441562276976</v>
+        <v>0.9305968286772557</v>
       </c>
       <c r="G73">
-        <v>-9.340231981709872</v>
+        <v>-7.110827851926174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.44035553721721</v>
       </c>
       <c r="E74">
-        <v>-19.16702190871682</v>
+        <v>-13.70972165428121</v>
       </c>
       <c r="F74">
-        <v>0.3254897213884053</v>
+        <v>0.6680880709576746</v>
       </c>
       <c r="G74">
-        <v>-9.495748168962676</v>
+        <v>-7.93891778148285</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.61029713173688</v>
       </c>
       <c r="E75">
-        <v>-19.88027920729494</v>
+        <v>-15.3385911124702</v>
       </c>
       <c r="F75">
-        <v>0.4727363625823034</v>
+        <v>0.326643451147803</v>
       </c>
       <c r="G75">
-        <v>-9.546810023360395</v>
+        <v>-7.478017010414437</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.74225840706525</v>
       </c>
       <c r="E76">
-        <v>-19.49582534946575</v>
+        <v>-13.73936051666141</v>
       </c>
       <c r="F76">
-        <v>0.5225328276814659</v>
+        <v>0.4657538032011309</v>
       </c>
       <c r="G76">
-        <v>-9.372817681452918</v>
+        <v>-7.858100743778162</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.83407894736124</v>
       </c>
       <c r="E77">
-        <v>-19.1462905547097</v>
+        <v>-15.35247088530371</v>
       </c>
       <c r="F77">
-        <v>0.1621858859178667</v>
+        <v>0.7923773112013626</v>
       </c>
       <c r="G77">
-        <v>-9.383527296272462</v>
+        <v>-7.775492700936728</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.88525338647954</v>
       </c>
       <c r="E78">
-        <v>-20.51908839318696</v>
+        <v>-14.82926005540549</v>
       </c>
       <c r="F78">
-        <v>0.4006729923120622</v>
+        <v>0.3404113985236758</v>
       </c>
       <c r="G78">
-        <v>-9.191287227352522</v>
+        <v>-8.748769915663683</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.89602639204782</v>
       </c>
       <c r="E79">
-        <v>-20.91289807831599</v>
+        <v>-15.72690323015392</v>
       </c>
       <c r="F79">
-        <v>0.4553821131609179</v>
+        <v>0.5007481609616387</v>
       </c>
       <c r="G79">
-        <v>-9.998984196387289</v>
+        <v>-7.784222609523786</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.86692394871033</v>
       </c>
       <c r="E80">
-        <v>-21.4999196354563</v>
+        <v>-14.71655086582858</v>
       </c>
       <c r="F80">
-        <v>0.465278691426499</v>
+        <v>0.198854220830994</v>
       </c>
       <c r="G80">
-        <v>-10.1294130695435</v>
+        <v>-7.797249606220818</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.79964929081143</v>
       </c>
       <c r="E81">
-        <v>-21.07918364387765</v>
+        <v>-17.14393973121211</v>
       </c>
       <c r="F81">
-        <v>0.2099932163872373</v>
+        <v>0.2109600688486131</v>
       </c>
       <c r="G81">
-        <v>-10.57597255733578</v>
+        <v>-7.796998004759834</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.69708182554031</v>
       </c>
       <c r="E82">
-        <v>-22.3173680640029</v>
+        <v>-16.75816808744669</v>
       </c>
       <c r="F82">
-        <v>0.3103787913962399</v>
+        <v>0.0616078906401383</v>
       </c>
       <c r="G82">
-        <v>-9.772436944043882</v>
+        <v>-8.060543914050134</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.56345534152007</v>
       </c>
       <c r="E83">
-        <v>-22.27524419878355</v>
+        <v>-17.83039299213883</v>
       </c>
       <c r="F83">
-        <v>0.1174446101007869</v>
+        <v>0.3593168878892342</v>
       </c>
       <c r="G83">
-        <v>-10.02781904803434</v>
+        <v>-8.046649554421814</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.40462312901141</v>
       </c>
       <c r="E84">
-        <v>-23.1083113341826</v>
+        <v>-19.82516767862159</v>
       </c>
       <c r="F84">
-        <v>0.3264977502035826</v>
+        <v>0.182925306733504</v>
       </c>
       <c r="G84">
-        <v>-9.915174425515099</v>
+        <v>-8.377992125810849</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.22802296721189</v>
       </c>
       <c r="E85">
-        <v>-24.95670309836742</v>
+        <v>-19.67585483364068</v>
       </c>
       <c r="F85">
-        <v>0.5322195649132513</v>
+        <v>0.08603021956213001</v>
       </c>
       <c r="G85">
-        <v>-9.938444250110637</v>
+        <v>-8.383679643047316</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.04237408087594</v>
       </c>
       <c r="E86">
-        <v>-24.85262518024913</v>
+        <v>-21.33925843461217</v>
       </c>
       <c r="F86">
-        <v>0.5061454307214562</v>
+        <v>0.5109203040565062</v>
       </c>
       <c r="G86">
-        <v>-9.673938282613948</v>
+        <v>-8.177290302492533</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.85489373337228</v>
       </c>
       <c r="E87">
-        <v>-26.67985085692209</v>
+        <v>-21.79508557127625</v>
       </c>
       <c r="F87">
-        <v>0.4598085711945712</v>
+        <v>0.08867975955866021</v>
       </c>
       <c r="G87">
-        <v>-9.782477828664492</v>
+        <v>-7.966670084738561</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.6710531292694</v>
       </c>
       <c r="E88">
-        <v>-28.49994418703298</v>
+        <v>-23.14764565941323</v>
       </c>
       <c r="F88">
-        <v>0.7495269802473173</v>
+        <v>0.4946619791286048</v>
       </c>
       <c r="G88">
-        <v>-10.13833830031737</v>
+        <v>-6.987639141864353</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.49336611328481</v>
       </c>
       <c r="E89">
-        <v>-29.92860075239485</v>
+        <v>-26.32211046726415</v>
       </c>
       <c r="F89">
-        <v>0.8047397195772829</v>
+        <v>0.07486113359349331</v>
       </c>
       <c r="G89">
-        <v>-9.161032151669122</v>
+        <v>-8.122709338186569</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.3229339288838</v>
       </c>
       <c r="E90">
-        <v>-30.29706004002895</v>
+        <v>-26.84701494644124</v>
       </c>
       <c r="F90">
-        <v>0.9089048087534817</v>
+        <v>0.1373779246054655</v>
       </c>
       <c r="G90">
-        <v>-9.662265299042478</v>
+        <v>-8.166103969115335</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.16081435068565</v>
       </c>
       <c r="E91">
-        <v>-33.32710728330126</v>
+        <v>-27.44862271836025</v>
       </c>
       <c r="F91">
-        <v>0.8584162641692721</v>
+        <v>0.3044446453310882</v>
       </c>
       <c r="G91">
-        <v>-10.02272080790386</v>
+        <v>-7.658282836118832</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.00897878497879</v>
       </c>
       <c r="E92">
-        <v>-35.14950787091905</v>
+        <v>-29.32911230631143</v>
       </c>
       <c r="F92">
-        <v>0.9874756266302634</v>
+        <v>0.7363948907964935</v>
       </c>
       <c r="G92">
-        <v>-9.375664750616691</v>
+        <v>-8.493232216032878</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.86998336698182</v>
       </c>
       <c r="E93">
-        <v>-37.61774583608877</v>
+        <v>-33.30466190188224</v>
       </c>
       <c r="F93">
-        <v>0.9087923656334854</v>
+        <v>0.4927829120599359</v>
       </c>
       <c r="G93">
-        <v>-9.508348105285142</v>
+        <v>-7.09103741069241</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.745502924663437</v>
       </c>
       <c r="E94">
-        <v>-38.61722080584769</v>
+        <v>-33.59875911783639</v>
       </c>
       <c r="F94">
-        <v>1.291365036214362</v>
+        <v>0.5701152719108441</v>
       </c>
       <c r="G94">
-        <v>-9.080837496525819</v>
+        <v>-7.848576304261679</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.63823380538585</v>
       </c>
       <c r="E95">
-        <v>-41.7314591736336</v>
+        <v>-36.95426325956596</v>
       </c>
       <c r="F95">
-        <v>1.21486728938089</v>
+        <v>0.6868201445254924</v>
       </c>
       <c r="G95">
-        <v>-9.613954507987893</v>
+        <v>-7.112224902143746</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.547593962250122</v>
       </c>
       <c r="E96">
-        <v>-42.94744954264726</v>
+        <v>-39.22730135263505</v>
       </c>
       <c r="F96">
-        <v>1.475502523002507</v>
+        <v>1.023859686331569</v>
       </c>
       <c r="G96">
-        <v>-9.12148106411145</v>
+        <v>-7.369709202551641</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.473116191116853</v>
       </c>
       <c r="E97">
-        <v>-45.44978238862073</v>
+        <v>-42.59177866561082</v>
       </c>
       <c r="F97">
-        <v>1.442274789190671</v>
+        <v>1.173793876463968</v>
       </c>
       <c r="G97">
-        <v>-9.485690731614369</v>
+        <v>-6.695370939475335</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.409882749387146</v>
       </c>
       <c r="E98">
-        <v>-47.62479034060876</v>
+        <v>-43.2589066637098</v>
       </c>
       <c r="F98">
-        <v>1.617068411077723</v>
+        <v>1.185549725474275</v>
       </c>
       <c r="G98">
-        <v>-9.659500993517186</v>
+        <v>-8.152302304762113</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.354782596831388</v>
       </c>
       <c r="E99">
-        <v>-49.84613363864329</v>
+        <v>-47.40008972458516</v>
       </c>
       <c r="F99">
-        <v>1.681287685948793</v>
+        <v>1.109694963242472</v>
       </c>
       <c r="G99">
-        <v>-9.160926214211866</v>
+        <v>-7.861308662405715</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.298744819961597</v>
       </c>
       <c r="E100">
-        <v>-52.81866473354418</v>
+        <v>-49.26689879255918</v>
       </c>
       <c r="F100">
-        <v>1.593295401581062</v>
+        <v>1.442920941204171</v>
       </c>
       <c r="G100">
-        <v>-9.51589945966022</v>
+        <v>-8.154341600814305</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.236921764585052</v>
       </c>
       <c r="E101">
-        <v>-54.41899688065534</v>
+        <v>-51.71541072495148</v>
       </c>
       <c r="F101">
-        <v>1.673731825026231</v>
+        <v>1.395325827327469</v>
       </c>
       <c r="G101">
-        <v>-9.606720965984586</v>
+        <v>-7.835211631919641</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.149781324392325</v>
       </c>
       <c r="E102">
-        <v>-57.81107297847085</v>
+        <v>-54.00240897126771</v>
       </c>
       <c r="F102">
-        <v>1.987242248046624</v>
+        <v>1.621995320180655</v>
       </c>
       <c r="G102">
-        <v>-9.579461934014226</v>
+        <v>-7.564577844629761</v>
       </c>
     </row>
   </sheetData>
